--- a/output/北塩原村_アンケート回収数の変更の影響.xlsx
+++ b/output/北塩原村_アンケート回収数の変更の影響.xlsx
@@ -4591,12 +4591,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>報告書用集計表の令和8年10月21日版（有効回答数40件）を拝見しました。設問ごとに最も多い選択肢は1件も入れ替わっておらず、課題の8区分・障がい児調査・障がい別の集計も動いていません。動いたのは数値だけです。正本 第2章7 の割合は素案の本文にあるものですので、新しい集計に合わせて差し替えていただけますでしょうか。当方が足した記述（9件）は当方で直します。なお、村が力を入れるべきこと（問44）は、新しい集計では相談支援体制37.5％・災害時支援35.0％となり同率でなくなります。「各34.2％」という書き方をされている箇所は言い回しの修正が要ります。</t>
+          <t>報告書用集計表の令和8年10月21日版（有効回答数40件）を拝見しました。設問ごとに最も多い選択肢は1件も入れ替わっておらず、課題の8区分・障がい児調査・障がい別の集計も動いていません。動いたのは数値だけです。正本 第2章7 の割合は素案の本文にあるものですので、新しい集計に合わせて差し替えていただけますでしょうか。当方が足した記述（9件）は当方で直します。なお、村が力を入れるべきこと（問44）は、新しい集計では相談支援体制37.5％・災害時支援35.0％となり同率でなくなります。「各34.2％」という書き方をされている箇所は言い回しの修正が要ります。なお、差し替えは報告書の直し残しの修正（Ｓ-40）の後にお願いいたします。直し残し11か所のうち4か所は、同じ文が正本の第2章7にあるためです（「北塩原村_報告書の修正方針と計画への影響.xlsx」の05シート）。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月30日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
     </row>
